--- a/项目推进计划表_v2.xlsx
+++ b/项目推进计划表_v2.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +50,12 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +80,12 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -95,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +129,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>计划周期：2026年6月1日 起 ｜ 单位：2天/阶段 ｜ 当前日期：2026-06-01</t>
+          <t>计划周期：2026年6月1日 起 ｜ 单位：2天/阶段 ｜ 当前日期：2026-06-12</t>
         </is>
       </c>
     </row>
@@ -593,10 +606,14 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>拼版工具接口若变更会阻塞P3</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
+          <t>需求冻结完成，环境准备就绪</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -634,8 +651,16 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>数据库迁移脚本已完成，PostgreSQL迁移成功</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -676,16 +701,12 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>6/5完成全部4个阶段
-配色：深蓝黑sidebar+金色点缀+纯色按钮</t>
+          <t>6/5完成全部4个阶段：plate_file上传、跨订单智能拼版、拖拽旋转、300DPI高清PDF</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>① plate_file上传
-② 跨订单智能拼版
-③ 拖拽旋转调整
-④ 300DPI高清PDF</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -726,10 +747,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>周末加班或视情况顺延</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>全链路自测、多角色权限验证、边界场景处理均已完成</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="88" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -766,10 +791,14 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>集成测试、性能测试、Bug修复闭环完成</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>★ 集成测试通过</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -810,12 +839,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>部署问题可能导致1天延期</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>★ 生产部署完成</t>
+          <t>Gunicorn+systemd+Nginx生产部署完成，系统可通过IP访问</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -858,12 +887,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>内测发现重大问题需追加修复时间</t>
+          <t>团队内测计划6/13启动</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>★ 团队内测完成</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -905,12 +934,12 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>客户时间协调风险</t>
+          <t>客户UAT测试计划6/15启动</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>★ 客户测试启动</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -951,10 +980,14 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>客户反馈修复与上线准备计划6/17启动</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>★ 系统具备上线条件</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -995,10 +1028,14 @@
           <t>未开始</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>正式上线/交付计划6/19-6/20</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>★ 正式上线交付</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
